--- a/data/panel_2020_2024.xlsx
+++ b/data/panel_2020_2024.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIDTERM_PROJECT\Team_2_FirmDataHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E6BE1D8-7108-465E-9E46-9845D4ED8D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFF47DC-3CF0-46CE-AAC6-15E48CF51C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9990" yWindow="0" windowWidth="11745" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="panel_2020_2024" sheetId="10" r:id="rId1"/>
@@ -4858,7 +4858,7 @@
         <v>12600</v>
       </c>
       <c r="I31" s="1">
-        <v>275580660000</v>
+        <v>347231631600</v>
       </c>
       <c r="J31" s="1">
         <v>-25524315183</v>
@@ -6353,7 +6353,7 @@
         <v>12516</v>
       </c>
       <c r="I42" s="1">
-        <v>2673840900000</v>
+        <v>3346579270440</v>
       </c>
       <c r="J42" s="1">
         <v>0</v>
@@ -6490,7 +6490,7 @@
         <v>19805</v>
       </c>
       <c r="I43" s="1">
-        <v>2673840900000</v>
+        <v>5295541902450</v>
       </c>
       <c r="J43" s="1">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>7297</v>
       </c>
       <c r="I44" s="1">
-        <v>3078044500000</v>
+        <v>2246049071650</v>
       </c>
       <c r="J44" s="1">
         <v>0</v>
@@ -6871,7 +6871,7 @@
       <c r="AV45" s="2"/>
       <c r="AW45" s="2"/>
     </row>
-    <row r="46" spans="1:49" ht="26.25" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:49" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>2</v>
       </c>
@@ -11582,7 +11582,7 @@
       <c r="AV80" s="2"/>
       <c r="AW80" s="2"/>
     </row>
-    <row r="81" spans="1:49" ht="26.25" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:49" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>15</v>
       </c>
@@ -12253,7 +12253,7 @@
       <c r="AV85" s="2"/>
       <c r="AW85" s="2"/>
     </row>
-    <row r="86" spans="1:49" ht="26.25" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:49" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>16</v>
       </c>
@@ -14210,7 +14210,7 @@
       <c r="AV100" s="2"/>
       <c r="AW100" s="2"/>
     </row>
-    <row r="101" spans="1:49" ht="26.25" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:49" ht="13.15" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>8</v>
       </c>
